--- a/data_extactor/batch_10_fa/trimmed/batch_0022_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0022_fa_trim.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>علوم پایه | درک مطلب | تفکر انتقادی | نگارش | شنیدن فعال | سخن گفتن | یادگیری فعال | نظارت | راهبردهای یادگیری | ریاضیات</t>
+          <t>علوم | درک مطلب | تفکر انتقادی | نگارش | گوش دادن فعال | سخن گفتن | یادگیری فعال | نظارت | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | شیمی | زبان انگلیسی | رایانه و الکترونیک | آموزش و تدریس | ریاضیات | مهندسی و فناوری</t>
+          <t>زیست‌شناسی | شیمی | زبان انگلیسی | رایانه و الکترونیک | آموزش و پرورش | ریاضیات | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک کتبی | بیان کتبی | استدلال استقرایی | حساسیت به مسئله | استدلال قیاسی | درک شفاهی | مرتب‌سازی اطلاعات</t>
+          <t>درک کتبی | بیان کتبی | استدلال استقرایی | حساسیت به مسئله | استدلال قیاسی | درک شفاهی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>بیوشیمیست‌ها و بیوفیزیکدان‌ها | تکنسین‌های زیست‌شناسی | زیست‌شناسان | اپیدمیولوژیست‌ها | دانشمندان علوم پزشکی، به جز اپیدمیولوژیست‌ها | کارشناسان آزمایشگاه پزشکی و بالینی | زیست‌شناسان سلولی و مولکولی</t>
+          <t>زیست‌شیمی‌دانان و زیست‌فیزیک‌دانان | تکنسین‌های علوم زیستی | زیست‌شناسان | متخصصان همه‌گیرشناسی و اپیدمیولوژیست‌ها | پژوهشگران و دانشمندان علوم پزشکی | کارشناسان علوم آزمایشگاهی بالینی | زیست‌شناسان سلولی و مولکولی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | شنیدن فعال | درک مطلب | نگارش | علوم پایه | یادگیری فعال | نظارت | ریاضیات | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | علوم | یادگیری فعال | نظارت | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | ریاضیات | جغرافیا | حقوق و مقررات دولتی | مدیریت و امور اداری | ارتباطات و رسانه</t>
+          <t>زیست‌شناسی | ریاضیات | جغرافیا | قانون و دولت | مدیریت و اداره | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | مرتب‌سازی اطلاعات</t>
+          <t>بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>تکنسین‌های زیست‌شناسی | زیست‌شناسان | دانشمندان حفاظت از منابع طبیعی | محیط‌بانان و حافظان شیلات و حیات وحش | تکنسین‌های جنگلداری و حفاظت از منابع طبیعی | جنگلداران | مدیران مراتع</t>
+          <t>تکنسین‌های علوم زیستی | زیست‌شناسان | دانشمندان حفاظت از منابع طبیعی | محیط‌بانان و ماموران حفاظت شیلات و حیات وحش | کاردان‌ها و تکنسین‌های جنگل‌داری و حفاظت منابع طبیعی | کارشناسان جنگل‌داری و جنگل‌بانان | مدیران و کارشناسان مدیریت مراتع</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,12 +622,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | ریاضیات | یادگیری فعال | نگارش | سخن گفتن | شنیدن فعال | علوم پایه | نظارت</t>
+          <t>درک مطلب | تفکر انتقادی | ریاضیات | یادگیری فعال | نگارش | سخن گفتن | گوش دادن فعال | علوم | نظارت</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | شیمی | ریاضیات | رایانه و الکترونیک | آموزش و تدریس | پزشکی و دندانپزشکی</t>
+          <t>زیست‌شناسی | شیمی | ریاضیات | رایانه و الکترونیک | آموزش و پرورش | پزشکی و دندان‌پزشکی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>جانورشناسان و زیست‌شناسان حیات وحش | میکروبیولوژیست‌ها | بیوشیمیست‌ها و بیوفیزیکدان‌ها | زیست‌شناسان سلولی و مولکولی | زیست‌شناسان | دانشمندان خاک‌شناسی و علوم گیاهی | تکنسین‌های زیست‌شناسی</t>
+          <t>جانورشناسان و زیست‌شناسان حیات وحش | میکروبیولوژیست‌ها | زیست‌شیمی‌دانان و زیست‌فیزیک‌دانان | زیست‌شناسان سلولی و مولکولی | زیست‌شناسان | متخصصان خاک‌شناسی و علوم گیاهی | تکنسین‌های علوم زیستی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,12 +679,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | سخن گفتن | شنیدن فعال | نگارش | علوم پایه | یادگیری فعال | ریاضیات | نظارت | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | درک مطلب | سخن گفتن | گوش دادن فعال | نگارش | علوم | یادگیری فعال | ریاضیات | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | رایانه و الکترونیک | ریاضیات | زبان انگلیسی | شیمی | آموزش و تدریس | امور دفتری و اداری</t>
+          <t>زیست‌شناسی | رایانه و الکترونیک | ریاضیات | زبان انگلیسی | شیمی | آموزش و پرورش | اداری</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>بیوشیمیست‌ها و بیوفیزیکدان‌ها | تکنسین‌های بیوانفورماتیک | متخصصان آمار زیستی | دانشمندان علوم داده | متخصصان ژنتیک | میکروبیولوژیست‌ها | زیست‌شناسان سلولی و مولکولی</t>
+          <t>زیست‌شیمی‌دانان و زیست‌فیزیک‌دانان | تکنسین‌های بیوانفورماتیک | کارشناسان آمار زیستی | دانشمندان داده | متخصصان ژنتیک | میکروبیولوژیست‌ها | زیست‌شناسان سلولی و مولکولی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,12 +736,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>علوم پایه | درک مطلب | نگارش | تفکر انتقادی | سخن گفتن | شنیدن فعال | یادگیری فعال | راهبردهای یادگیری | ریاضیات | نظارت</t>
+          <t>علوم | درک مطلب | نگارش | تفکر انتقادی | سخن گفتن | گوش دادن فعال | یادگیری فعال | راهبردهای یادگیری | ریاضیات | نظارت</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | زبان انگلیسی | شیمی | ریاضیات | آموزش و تدریس | رایانه و الکترونیک | پزشکی و دندانپزشکی</t>
+          <t>زیست‌شناسی | زبان انگلیسی | شیمی | ریاضیات | آموزش و پرورش | رایانه و الکترونیک | پزشکی و دندان‌پزشکی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>بیوشیمیست‌ها و بیوفیزیکدان‌ها | متخصصان بیوانفورماتیک | تکنسین‌های زیست‌شناسی | متخصصان ژنتیک | دانشمندان علوم پزشکی، به جز اپیدمیولوژیست‌ها | کارشناسان آزمایشگاه پزشکی و بالینی | میکروبیولوژیست‌ها</t>
+          <t>زیست‌شیمی‌دانان و زیست‌فیزیک‌دانان | متخصصان بیوانفورماتیک | تکنسین‌های علوم زیستی | متخصصان ژنتیک | پژوهشگران و دانشمندان علوم پزشکی | کارشناسان علوم آزمایشگاهی بالینی | میکروبیولوژیست‌ها</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,12 +793,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | علوم پایه | یادگیری فعال | تفکر انتقادی | سخن گفتن | نگارش | شنیدن فعال | ریاضیات | راهبردهای یادگیری | نظارت</t>
+          <t>درک مطلب | علوم | یادگیری فعال | تفکر انتقادی | سخن گفتن | نگارش | گوش دادن فعال | ریاضیات | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | زبان انگلیسی | آموزش و تدریس | ریاضیات | شیمی | رایانه و الکترونیک</t>
+          <t>زیست‌شناسی | زبان انگلیسی | آموزش و پرورش | ریاضیات | شیمی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>بیوشیمیست‌ها و بیوفیزیکدان‌ها | متخصصان بیوانفورماتیک | متخصصان آمار زیستی | اپیدمیولوژیست‌ها | مشاوران ژنتیک | کارشناسان آزمایشگاه پزشکی و بالینی | زیست‌شناسان سلولی و مولکولی</t>
+          <t>زیست‌شیمی‌دانان و زیست‌فیزیک‌دانان | متخصصان بیوانفورماتیک | کارشناسان آمار زیستی | متخصصان همه‌گیرشناسی و اپیدمیولوژیست‌ها | مشاوران ژنتیک | کارشناسان علوم آزمایشگاهی بالینی | زیست‌شناسان سلولی و مولکولی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>علوم پایه | درک مطلب | نگارش | شنیدن فعال | تفکر انتقادی | سخن گفتن | ریاضیات | یادگیری فعال | راهبردهای یادگیری | نظارت</t>
+          <t>علوم | درک مطلب | نگارش | گوش دادن فعال | تفکر انتقادی | سخن گفتن | ریاضیات | یادگیری فعال | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | آموزش و تدریس | ریاضیات | مدیریت و امور اداری | شیمی | مهندسی و فناوری</t>
+          <t>زیست‌شناسی | آموزش و پرورش | ریاضیات | مدیریت و اداره | شیمی | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان کتبی | استدلال استقرایی | بیان شفاهی | مرتب‌سازی اطلاعات | استدلال قیاسی</t>
+          <t>درک شفاهی | درک کتبی | بیان کتبی | استدلال استقرایی | بیان شفاهی | ترتیب‌دهی اطلاعات | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>بیوشیمیست‌ها و بیوفیزیکدان‌ها | تکنسین‌های زیست‌شناسی | دانشمندان حفاظت از منابع طبیعی | دانشمندان و متخصصان محیط زیست، از جمله بهداشت محیط | متخصصان ژنتیک | میکروبیولوژیست‌ها | جانورشناسان و زیست‌شناسان حیات وحش</t>
+          <t>زیست‌شیمی‌دانان و زیست‌فیزیک‌دانان | تکنسین‌های علوم زیستی | دانشمندان حفاظت از منابع طبیعی | کارشناسان و متخصصان علوم محیطی (شامل بهداشت) | متخصصان ژنتیک | میکروبیولوژیست‌ها | جانورشناسان و زیست‌شناسان حیات وحش</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | سخن گفتن | نگارش | علوم پایه | تفکر انتقادی | نظارت | یادگیری فعال | ریاضیات</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | نگارش | علوم | تفکر انتقادی | نظارت | یادگیری فعال | ریاضیات</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | جغرافیا | ریاضیات | شیمی | حقوق و مقررات دولتی | مهندسی و فناوری</t>
+          <t>زیست‌شناسی | جغرافیا | ریاضیات | شیمی | قانون و دولت | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | مرتب‌سازی اطلاعات | بیان کتبی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات | بیان کتبی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مهندسان کشاورزی | برنامه‌ریزان احیای محیط زیست | دانشمندان و متخصصان محیط زیست، از جمله بهداشت محیط | تکنسین‌های جنگلداری و حفاظت از منابع طبیعی | جنگلداران | مدیران مراتع | دانشمندان خاک‌شناسی و علوم گیاهی</t>
+          <t>مهندسان کشاورزی | برنامه‌ریزان احیای محیط زیست | کارشناسان و متخصصان علوم محیطی (شامل بهداشت) | کاردان‌ها و تکنسین‌های جنگل‌داری و حفاظت منابع طبیعی | کارشناسان جنگل‌داری و جنگل‌بانان | مدیران و کارشناسان مدیریت مراتع | متخصصان خاک‌شناسی و علوم گیاهی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,12 +964,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | نظارت | یادگیری فعال | نگارش</t>
+          <t>گوش دادن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | جغرافیا | حقوق و مقررات دولتی | مدیریت و امور اداری | رایانه و الکترونیک | ریاضیات</t>
+          <t>زیست‌شناسی | جغرافیا | قانون و دولت | مدیریت و اداره | رایانه و الکترونیک | ریاضیات</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>دانشمندان حفاظت از منابع طبیعی | سرپرستان رده‌اول کارگران کشاورزی، صیادی و جنگلداری | محیط‌بانان و حافظان شیلات و حیات وحش | تکنسین‌های جنگلداری و حفاظت از منابع طبیعی | جنگلداران | دانشمندان خاک‌شناسی و علوم گیاهی | جانورشناسان و زیست‌شناسان حیات وحش</t>
+          <t>دانشمندان حفاظت از منابع طبیعی | سرپرستان رده‌اول کارگران کشاورزی، شیلات و جنگل‌داری | محیط‌بانان و ماموران حفاظت شیلات و حیات وحش | کاردان‌ها و تکنسین‌های جنگل‌داری و حفاظت منابع طبیعی | کارشناسان جنگل‌داری و جنگل‌بانان | متخصصان خاک‌شناسی و علوم گیاهی | جانورشناسان و زیست‌شناسان حیات وحش</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>سخن گفتن | درک مطلب | شنیدن فعال | نگارش | تفکر انتقادی | راهبردهای یادگیری | یادگیری فعال | نظارت</t>
+          <t>سخن گفتن | درک مطلب | گوش دادن فعال | نگارش | تفکر انتقادی | راهبردهای یادگیری | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | آموزش و تدریس | ایمنی و امنیت عمومی | زیست‌شناسی | ارتباطات و رسانه | جغرافیا</t>
+          <t>خدمات مشتری و شخصی | آموزش و پرورش | ایمنی و امنیت عمومی | زیست‌شناسی | ارتباطات و رسانه | جغرافیا</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | حساسیت به مسئله | مرتب‌سازی اطلاعات</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | حساسیت به مسئله | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>دانشمندان حفاظت از منابع طبیعی | محیط‌بانان و حافظان شیلات و حیات وحش | تکنسین‌های جنگلداری و حفاظت از منابع طبیعی | جنگلداران | کارکنان خدمات تفریحی و اوقات فراغت | راهنمایان تور و گردشگری | جانورشناسان و زیست‌شناسان حیات وحش</t>
+          <t>دانشمندان حفاظت از منابع طبیعی | محیط‌بانان و ماموران حفاظت شیلات و حیات وحش | کاردان‌ها و تکنسین‌های جنگل‌داری و حفاظت منابع طبیعی | کارشناسان جنگل‌داری و جنگل‌بانان | کارکنان و متصدیان امور تفریحی و اوقات فراغت | راهنمایان تور و گردشگری | جانورشناسان و زیست‌شناسان حیات وحش</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
